--- a/sheets/대금율보/검수/시계바늘.xlsx
+++ b/sheets/대금율보/검수/시계바늘.xlsx
@@ -4820,7 +4820,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C5" s="23"/>
@@ -4851,7 +4851,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-汰㳞‹</t>
+汰㳞</t>
         </is>
       </c>
       <c r="K5" s="23"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢汰</t>
         </is>
       </c>
@@ -5037,7 +5037,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞淋</t>
         </is>
       </c>
@@ -5087,7 +5087,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 –潢</t>
         </is>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="I12" s="23"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞淋</t>
         </is>
       </c>
@@ -5221,13 +5221,13 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-南潢‹</t>
+南潢</t>
         </is>
       </c>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞淋</t>
         </is>
       </c>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K17" s="23"/>
@@ -5433,7 +5433,7 @@
       <c r="D19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰潢‹</t>
+汰潢</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">

--- a/sheets/대금율보/검수/시계바늘.xlsx
+++ b/sheets/대금율보/검수/시계바늘.xlsx
@@ -4693,22 +4693,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="121.21" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.45" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.45" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.45" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.45" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.45" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.45" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.45" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.45" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.45" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.45" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.45" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.45" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="90.45" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="90.45" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="90.45" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="25" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="90.45" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="K18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="90.45" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="90.45" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -5500,7 +5500,7 @@
       <c r="J20" s="21"/>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="90.45" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="90.45" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="25" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="90.45" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="90.45" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="90.45" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="90.45" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="24"/>
@@ -5759,6 +5759,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="33"/>
 </worksheet>
 </file>